--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOSPITAL OCHOA CB MARBELLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HOSPITAL OCHOA CB MARBELLA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>83.9777</v>
+        <v>63.1468</v>
       </c>
       <c r="E2" t="n">
-        <v>64.03100000000001</v>
+        <v>48.0008</v>
       </c>
       <c r="F2" t="n">
-        <v>19.9464</v>
+        <v>15.1464</v>
       </c>
       <c r="G2" t="n">
         <v>22.6755</v>
@@ -610,13 +610,13 @@
         <v>46.1863</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6423</v>
+        <v>10.8118</v>
       </c>
       <c r="T2" t="n">
-        <v>23.9421</v>
+        <v>7.9118</v>
       </c>
       <c r="U2" t="n">
-        <v>7.7</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>15.7839</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>41.3889</v>
+        <v>53.9963</v>
       </c>
       <c r="E3" t="n">
-        <v>30.2534</v>
+        <v>37.9359</v>
       </c>
       <c r="F3" t="n">
-        <v>11.1354</v>
+        <v>16.0603</v>
       </c>
       <c r="G3" t="n">
         <v>45.9865</v>
@@ -688,13 +688,13 @@
         <v>49.5558</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.3977</v>
+        <v>-6.7906</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.8361</v>
+        <v>-3.1537</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.561500000000001</v>
+        <v>-3.6368</v>
       </c>
       <c r="V3" t="n">
         <v>22.3322</v>
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>40.2292</v>
+        <v>38.6028</v>
       </c>
       <c r="E4" t="n">
-        <v>38.8597</v>
+        <v>38.1593</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3694</v>
+        <v>0.4437</v>
       </c>
       <c r="G4" t="n">
         <v>25.5977</v>
@@ -766,13 +766,13 @@
         <v>16.6508</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6936</v>
+        <v>3.0675</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0285</v>
+        <v>1.3282</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6655</v>
+        <v>1.7393</v>
       </c>
       <c r="V4" t="n">
         <v>15.2902</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>17.9002</v>
+        <v>16.8791</v>
       </c>
       <c r="E6" t="n">
-        <v>18.022</v>
+        <v>20.5748</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1217000000000005</v>
+        <v>-3.6957</v>
       </c>
       <c r="G6" t="n">
-        <v>13.333</v>
+        <v>11.9757</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2473</v>
+        <v>6.5597</v>
       </c>
       <c r="I6" t="n">
-        <v>10.086</v>
+        <v>5.4159</v>
       </c>
       <c r="J6" t="n">
-        <v>25.0796</v>
+        <v>21.342</v>
       </c>
       <c r="K6" t="n">
-        <v>9.042299999999999</v>
+        <v>13.4098</v>
       </c>
       <c r="L6" t="n">
-        <v>16.0373</v>
+        <v>7.931999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.7467</v>
+        <v>-9.366299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.795199999999999</v>
+        <v>-6.8504</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.9515</v>
+        <v>-2.516</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.5679</v>
+        <v>4.5591</v>
       </c>
       <c r="Q6" t="n">
-        <v>-18.8309</v>
+        <v>-16.4524</v>
       </c>
       <c r="R6" t="n">
-        <v>15.2631</v>
+        <v>21.0116</v>
       </c>
       <c r="S6" t="n">
-        <v>7.9019</v>
+        <v>-4.5464</v>
       </c>
       <c r="T6" t="n">
-        <v>7.156300000000001</v>
+        <v>-1.0582</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7456</v>
+        <v>-3.4882</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2333999999999998</v>
+        <v>4.890600000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>4.6173</v>
+        <v>16.7438</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.383900000000001</v>
+        <v>-11.8529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>13.5802</v>
+        <v>14.0512</v>
       </c>
       <c r="E7" t="n">
-        <v>13.5802</v>
+        <v>12.9185</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.1328</v>
       </c>
       <c r="G7" t="n">
-        <v>13.5802</v>
+        <v>13.333</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5402</v>
+        <v>3.2473</v>
       </c>
       <c r="I7" t="n">
-        <v>9.040100000000001</v>
+        <v>10.086</v>
       </c>
       <c r="J7" t="n">
-        <v>13.5802</v>
+        <v>25.0796</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5402</v>
+        <v>9.042299999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9.040100000000001</v>
+        <v>16.0373</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-11.7467</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-5.795199999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-5.9515</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.5679</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-18.8309</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>15.2631</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.0527</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.0526</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.9999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2333999999999998</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.6173</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-4.383900000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>9.626299999999999</v>
+        <v>13.5802</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2899</v>
+        <v>13.5802</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.6635</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11.9757</v>
+        <v>13.5802</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5597</v>
+        <v>4.5402</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4159</v>
+        <v>9.040100000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>21.342</v>
+        <v>13.5802</v>
       </c>
       <c r="K8" t="n">
-        <v>13.4098</v>
+        <v>4.5402</v>
       </c>
       <c r="L8" t="n">
-        <v>7.931999999999999</v>
+        <v>9.040100000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-9.366299999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.8504</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.516</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5591</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.4524</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>21.0116</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-11.7992</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.343</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.4562</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.890600000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>16.7438</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.8529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>3.036799999999999</v>
+        <v>6.606899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2785000000000002</v>
+        <v>4.478</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7581</v>
+        <v>2.129100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6879</v>
+        <v>15.9128</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9313</v>
+        <v>7.66</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2431</v>
+        <v>8.252599999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>5.834</v>
+        <v>36.4909</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2404</v>
+        <v>23.9139</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5937</v>
+        <v>12.577</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.146</v>
+        <v>-20.578</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.3094</v>
+        <v>-16.2537</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8367000000000002</v>
+        <v>-4.3242</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7663</v>
+        <v>-3.5681</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.92</v>
+        <v>-49.9517</v>
       </c>
       <c r="R9" t="n">
-        <v>5.1538</v>
+        <v>46.3841</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6015</v>
+        <v>-7.607699999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1119</v>
+        <v>-7.027900000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7132</v>
+        <v>-0.5797000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>4.513500000000001</v>
+        <v>1.8701</v>
       </c>
       <c r="W9" t="n">
-        <v>4.4763</v>
+        <v>24.9671</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0371999999999999</v>
+        <v>-23.0973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2834</v>
+        <v>3.7016</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1199</v>
+        <v>1.1164</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8363</v>
+        <v>2.5851</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2986</v>
+        <v>1.6879</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3386999999999998</v>
+        <v>1.9313</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9599</v>
+        <v>-0.2431</v>
       </c>
       <c r="J10" t="n">
-        <v>8.1587</v>
+        <v>5.834</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1371</v>
+        <v>5.2404</v>
       </c>
       <c r="L10" t="n">
-        <v>4.0217</v>
+        <v>0.5937</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8603</v>
+        <v>-4.146</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.7985</v>
+        <v>-3.3094</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0616000000000001</v>
+        <v>-0.8367000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-3.7663</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.9555</v>
+        <v>-8.92</v>
       </c>
       <c r="R10" t="n">
-        <v>4.9554</v>
+        <v>5.1538</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1734999999999999</v>
+        <v>1.2663</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4428</v>
+        <v>-0.2738</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2693</v>
+        <v>1.5401</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1888</v>
+        <v>4.513500000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4737</v>
+        <v>4.4763</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.6625</v>
+        <v>0.0371999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. TRIGO VILLALBA</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08360000000000001</v>
+        <v>0.8711000000000007</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1782</v>
+        <v>5.0617</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2618</v>
+        <v>-4.1906</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1523</v>
+        <v>4.2986</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6093</v>
+        <v>0.3386999999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7616000000000001</v>
+        <v>3.9599</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1892</v>
+        <v>8.1587</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6791</v>
+        <v>4.1371</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4899</v>
+        <v>4.0217</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3415</v>
+        <v>-3.8603</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0698</v>
+        <v>-3.7985</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2717</v>
+        <v>-0.0616000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.9555</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.9554</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06870000000000001</v>
+        <v>-0.2387000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01100000000000001</v>
+        <v>0.385</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.6233</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-3.1888</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-4.6625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. BALLESTA GARRIDO</t>
+          <t>E. TRIGO VILLALBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,61 +1342,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0658</v>
+        <v>0.2698</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2315</v>
+        <v>-0.07630000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1656</v>
+        <v>0.3461</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0457</v>
+        <v>0.1523</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3632</v>
+        <v>-0.6093</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3175</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0805</v>
+        <v>-0.1892</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0404</v>
+        <v>-0.6791</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>0.4899</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1262</v>
+        <v>0.3415</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4036</v>
+        <v>0.0698</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2774</v>
+        <v>0.2717</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2184</v>
+        <v>0.1175</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.312</v>
+        <v>0.1129</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0936</v>
+        <v>0.0046</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MARKOTA</t>
+          <t>C. BALLESTA GARRIDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5038</v>
+        <v>0.1764</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0641</v>
+        <v>-0.1296</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5603</v>
+        <v>0.306</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.796</v>
+        <v>-0.0457</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5522</v>
+        <v>-0.3632</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3482</v>
+        <v>0.3175</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0364</v>
+        <v>0.0805</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5535</v>
+        <v>0.0404</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.5898</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2404000000000002</v>
+        <v>-0.1262</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0014</v>
+        <v>-0.4036</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2417</v>
+        <v>0.2774</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3964999999999999</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.9377</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7.3342</v>
+        <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0904</v>
+        <v>0.0239</v>
       </c>
       <c r="T13" t="n">
-        <v>1.392</v>
+        <v>-0.2101</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6984</v>
+        <v>0.234</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.1947</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5181</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.712800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>A. FIDALGO PEDUZZI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0024</v>
+        <v>-1.4963</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.345999999999999</v>
+        <v>-5.414499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3433000000000003</v>
+        <v>3.9181</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9215</v>
+        <v>7.9892</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.614800000000001</v>
+        <v>0.01119999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6932</v>
+        <v>7.9781</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4281</v>
+        <v>6.9845</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5186</v>
+        <v>0.6934</v>
       </c>
       <c r="L14" t="n">
-        <v>5.9103</v>
+        <v>6.2911</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.3501</v>
+        <v>1.0046</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.1326</v>
+        <v>-0.6823</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2169</v>
+        <v>1.687</v>
       </c>
       <c r="P14" t="n">
-        <v>13.6773</v>
+        <v>-5.7485</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.9021</v>
+        <v>-10.9022</v>
       </c>
       <c r="R14" t="n">
-        <v>24.5795</v>
+        <v>5.1538</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2295</v>
+        <v>-0.7645000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4953</v>
+        <v>-1.7633</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2651999999999998</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-13.9885</v>
+        <v>-2.9725</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3670999999999999</v>
+        <v>0.2666</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.6214</v>
+        <v>-3.2391</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FIDALGO PEDUZZI</t>
+          <t>P. MARKOTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1029</v>
+        <v>-2.1694</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.0257</v>
+        <v>-8.365500000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9227</v>
+        <v>6.1959</v>
       </c>
       <c r="G15" t="n">
-        <v>7.9892</v>
+        <v>-1.796</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01119999999999999</v>
+        <v>1.5522</v>
       </c>
       <c r="I15" t="n">
-        <v>7.9781</v>
+        <v>-3.3482</v>
       </c>
       <c r="J15" t="n">
-        <v>6.9845</v>
+        <v>-2.0364</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6934</v>
+        <v>3.5535</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2911</v>
+        <v>-5.5898</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0046</v>
+        <v>0.2404000000000002</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6823</v>
+        <v>-2.0014</v>
       </c>
       <c r="O15" t="n">
-        <v>1.687</v>
+        <v>2.2417</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.7485</v>
+        <v>0.3964999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10.9022</v>
+        <v>-6.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>5.1538</v>
+        <v>7.3342</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3712</v>
+        <v>3.4248</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.3746</v>
+        <v>0.09060000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0034</v>
+        <v>3.3342</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.9725</v>
+        <v>-4.1947</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2666</v>
+        <v>0.5181</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.2391</v>
+        <v>-4.712800000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.714300000000001</v>
+        <v>-5.337100000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.341399999999998</v>
+        <v>7.235399999999998</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6269</v>
+        <v>-12.5723</v>
       </c>
       <c r="G16" t="n">
-        <v>15.9128</v>
+        <v>-7.0242</v>
       </c>
       <c r="H16" t="n">
-        <v>7.66</v>
+        <v>-19.4655</v>
       </c>
       <c r="I16" t="n">
-        <v>8.252599999999999</v>
+        <v>12.4413</v>
       </c>
       <c r="J16" t="n">
-        <v>36.4909</v>
+        <v>16.6364</v>
       </c>
       <c r="K16" t="n">
-        <v>23.9139</v>
+        <v>-1.8104</v>
       </c>
       <c r="L16" t="n">
-        <v>12.577</v>
+        <v>18.447</v>
       </c>
       <c r="M16" t="n">
-        <v>-20.578</v>
+        <v>-23.6605</v>
       </c>
       <c r="N16" t="n">
-        <v>-16.2537</v>
+        <v>-17.6551</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.3242</v>
+        <v>-6.0057</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.5681</v>
+        <v>10.1094</v>
       </c>
       <c r="Q16" t="n">
-        <v>-49.9517</v>
+        <v>-26.7597</v>
       </c>
       <c r="R16" t="n">
-        <v>46.3841</v>
+        <v>36.8695</v>
       </c>
       <c r="S16" t="n">
-        <v>-16.929</v>
+        <v>-4.589</v>
       </c>
       <c r="T16" t="n">
-        <v>-15.847</v>
+        <v>-3.9466</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0818</v>
+        <v>-0.6424000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8701</v>
+        <v>-3.833600000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>24.9671</v>
+        <v>21.3057</v>
       </c>
       <c r="X16" t="n">
-        <v>-23.0973</v>
+        <v>-25.1392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.5356</v>
+        <v>-5.709000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.768799999999999</v>
+        <v>-6.9983</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.7668</v>
+        <v>1.2897</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.9012</v>
+        <v>-2.9215</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5143</v>
+        <v>-5.614800000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.4152</v>
+        <v>2.6932</v>
       </c>
       <c r="J17" t="n">
-        <v>7.5936</v>
+        <v>7.4281</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8348</v>
+        <v>1.5186</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7589</v>
+        <v>5.9103</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.4945</v>
+        <v>-10.3501</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.3205</v>
+        <v>-7.1326</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.1741</v>
+        <v>-3.2169</v>
       </c>
       <c r="P17" t="n">
-        <v>5.1538</v>
+        <v>13.6773</v>
       </c>
       <c r="Q17" t="n">
-        <v>-12.8843</v>
+        <v>-10.9021</v>
       </c>
       <c r="R17" t="n">
-        <v>18.0382</v>
+        <v>24.5795</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.234</v>
+        <v>-2.476300000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6740999999999999</v>
+        <v>-3.1571</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5603</v>
+        <v>0.6808000000000002</v>
       </c>
       <c r="V17" t="n">
-        <v>-11.5541</v>
+        <v>-13.9885</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1961</v>
+        <v>-0.3670999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.7502</v>
+        <v>-13.6214</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.7277</v>
+        <v>-7.496199999999998</v>
       </c>
       <c r="E18" t="n">
-        <v>-25.3947</v>
+        <v>-18.6127</v>
       </c>
       <c r="F18" t="n">
-        <v>8.667300000000001</v>
+        <v>11.1164</v>
       </c>
       <c r="G18" t="n">
         <v>-17.1611</v>
@@ -1858,13 +1858,13 @@
         <v>47.1769</v>
       </c>
       <c r="S18" t="n">
-        <v>-18.8966</v>
+        <v>-9.664999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-14.8776</v>
+        <v>-8.095800000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.0188</v>
+        <v>-1.5693</v>
       </c>
       <c r="V18" t="n">
         <v>18.3388</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-18.5875</v>
+        <v>-11.296</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.3942</v>
+        <v>-5.049300000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.1933</v>
+        <v>-6.2467</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.2746</v>
+        <v>-3.9012</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.3022</v>
+        <v>1.5143</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.9723</v>
+        <v>-5.4152</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6495</v>
+        <v>7.5936</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6722</v>
+        <v>5.8348</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0228</v>
+        <v>1.7589</v>
       </c>
       <c r="M19" t="n">
-        <v>-8.924100000000001</v>
+        <v>-11.4945</v>
       </c>
       <c r="N19" t="n">
-        <v>-6.9745</v>
+        <v>-4.3205</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9499</v>
+        <v>-7.1741</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.532500000000001</v>
+        <v>5.1538</v>
       </c>
       <c r="Q19" t="n">
-        <v>-25.7688</v>
+        <v>-12.8843</v>
       </c>
       <c r="R19" t="n">
-        <v>18.2364</v>
+        <v>18.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>4.0318</v>
+        <v>-0.9946999999999998</v>
       </c>
       <c r="T19" t="n">
-        <v>5.0569</v>
+        <v>0.04560000000000008</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0253</v>
+        <v>-1.0402</v>
       </c>
       <c r="V19" t="n">
-        <v>-8.8119</v>
+        <v>-11.5541</v>
       </c>
       <c r="W19" t="n">
-        <v>5.6685</v>
+        <v>0.1961</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.4803</v>
+        <v>-11.7502</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-23.6819</v>
+        <v>-21.8291</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.234900000000001</v>
+        <v>-16.5351</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.4466</v>
+        <v>-5.294</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.0242</v>
+        <v>-6.2746</v>
       </c>
       <c r="H20" t="n">
-        <v>-19.4655</v>
+        <v>-3.3022</v>
       </c>
       <c r="I20" t="n">
-        <v>12.4413</v>
+        <v>-2.9723</v>
       </c>
       <c r="J20" t="n">
-        <v>16.6364</v>
+        <v>2.6495</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8104</v>
+        <v>3.6722</v>
       </c>
       <c r="L20" t="n">
-        <v>18.447</v>
+        <v>-1.0228</v>
       </c>
       <c r="M20" t="n">
-        <v>-23.6605</v>
+        <v>-8.924100000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-17.6551</v>
+        <v>-6.9745</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.0057</v>
+        <v>-1.9499</v>
       </c>
       <c r="P20" t="n">
-        <v>10.1094</v>
+        <v>-7.532500000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-26.7597</v>
+        <v>-25.7688</v>
       </c>
       <c r="R20" t="n">
-        <v>36.8695</v>
+        <v>18.2364</v>
       </c>
       <c r="S20" t="n">
-        <v>-22.9333</v>
+        <v>0.7899</v>
       </c>
       <c r="T20" t="n">
-        <v>-16.4167</v>
+        <v>0.9158000000000002</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.5167</v>
+        <v>-0.1261000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.833600000000001</v>
+        <v>-8.8119</v>
       </c>
       <c r="W20" t="n">
-        <v>21.3057</v>
+        <v>5.6685</v>
       </c>
       <c r="X20" t="n">
-        <v>-25.1392</v>
+        <v>-14.4803</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>155.5284</v>
+        <v>178.8931</v>
       </c>
       <c r="E21" t="n">
-        <v>141.7991</v>
+        <v>150.2237</v>
       </c>
       <c r="F21" t="n">
-        <v>13.729</v>
+        <v>28.6703</v>
       </c>
       <c r="G21" t="n">
         <v>146.4091</v>
       </c>
       <c r="H21" t="n">
-        <v>30.7343</v>
+        <v>30.73429999999999</v>
       </c>
       <c r="I21" t="n">
         <v>115.6763</v>
@@ -2092,13 +2092,13 @@
         <v>362.7476</v>
       </c>
       <c r="S21" t="n">
-        <v>-37.4836</v>
+        <v>-14.1185</v>
       </c>
       <c r="T21" t="n">
-        <v>-24.2681</v>
+        <v>-15.844</v>
       </c>
       <c r="U21" t="n">
-        <v>-13.2151</v>
+        <v>1.725699999999999</v>
       </c>
       <c r="V21" t="n">
         <v>34.7086</v>
